--- a/utility_core/static/src/Transformer_Migration_Template.xlsx
+++ b/utility_core/static/src/Transformer_Migration_Template.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المحولات" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="بيانات التهيئة" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعليمات الاستيراد" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,21 +29,39 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="005D4037"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +70,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="001A237E"/>
+        <bgColor rgb="001A237E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+        <bgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+        <bgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8BBD0"/>
+        <bgColor rgb="00F8BBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1BEE7"/>
+        <bgColor rgb="00E1BEE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F7FA"/>
+        <bgColor rgb="00E0F7FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,33 +127,71 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B0BEC5"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B0BEC5"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B0BEC5"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00B0BEC5"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,298 +557,383 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="63" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="75" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="39" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="75" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="45" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="152" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="73" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>نموذج استيراد المحولات - نظام توزيع الكهرباء (Utility ERP)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>يرجى التاكد من ملء جميع الخانات المعتمدة  |  هل فعال يقبل: نعم / لا  |  رموز المنطقة والفرع تاتي من جدول الترميز  |  الخلية المغذية تطابق عداد الخلية</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>بيانات المكان والترميز والحالة</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>بيانات المحول والشريك</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>بيانات عداد الرصد والقراءة</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>ربط الخلية المغذية</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>المرجع</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>رمز المنطقة *</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>رمز الفرع *</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>هل فعال؟ *</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>رمز المحول *</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>اسم المحول *</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>رقم عداد رصد المحول</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>معامل الضرب للعداد</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>القراءة الحالية</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>إجمالي الاستهلاك</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>حالة الصورة</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>رقم عداد الخلية المغذية</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>معامل ضرب عداد الخلية</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>المرجع</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>الوصف</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>HOD</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>THT</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>827452</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>محول عام السوق - التحيتا</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>25701411610</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>34809</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>واضح</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>H1120-3060</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t>[1139] عداد رصد 25701411610 - محول عام السوق - التحيتا - منطقة الحديدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>HOD</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>ZBD</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>688745</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>عداد رصد محول جوار المديرية - زبيد</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>25701407782</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>305524</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>واضح</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>587777</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>[1049] 25701407782 - عداد رصد محول جوار المديرية - زبيد</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>قالب استيراد وتهيئة المحولات من النظام السابق - Utility ERP</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>قواعد ملء نموذج المحولات</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>رمز المنطقة</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>رمز الفرع</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/المعرف</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/اسم العرض</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/رقم العداد</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/معامل الضرب للعداد</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>القراءه السابقة</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>القراءه الحالية</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>اجمالي الاستهلاك</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>حاله الصوره</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>تاريخ القراءه</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>وصف</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/قراءه العداد بدايه الاشتراك</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/خلية إحتساب</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/الحساب التحليلي</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/العميل/الاسم</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>الخليه/معامل الضرب للعداد</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>الخليه/رقم العداد</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Analytic Account/مرجع</t>
-        </is>
-      </c>
+      <c r="A2" s="17" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>HOD</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>THT</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>827452</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[1139] عداد رصد 25701411610 - محول عام السوق - التحيتا - منطقة الحديدة </t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>25701411610</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>26494</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>34809</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>واضح</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 02:05:05</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[1139] عداد رصد 25701411610 - محول عام السوق - التحيتا - منطقة الحديدة </t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>عداد رصد 25701411610</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">محول عام السوق - التحيتا - منطقة الحديدة </t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>1139</t>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>1. الحقول المشار إليها بعلامة (*) إلزامية.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>HOD</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ZBD</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>688745</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>[1049] 25701407782 - عداد رصد محول جوار المديرية - زبيد</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>25701407782</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>290406</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>305524</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>واضح</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 02:05:05</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>[1049] 25701407782 - عداد رصد محول جوار المديرية - زبيد</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>25701407782</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>عداد رصد محول جوار المديرية - زبيد</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>587777</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1049</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>2. حقل هل فعال يقبل القيمتين: نعم أو لا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>3. رمزا المنطقة والفرع يجب أن يطابقا جدول الترميز الموجود في النظام.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>4. المرجع يحتوي على كود المرجع للمحول التابع للفيدر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>5. رقم عداد الخلية المغذية يُستخدم لربط المحول بالفيدر/الخلية المغذية له.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>6. أرقام العدادات وقيم القراءات الحالية والمعاملات تُدخل بالأرقام فقط.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/utility_core/static/src/Transformer_Migration_Template.xlsx
+++ b/utility_core/static/src/Transformer_Migration_Template.xlsx
@@ -560,7 +560,7 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="152" customWidth="1" min="1" max="1"/>
+    <col width="162" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -599,7 +599,7 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>يرجى التاكد من ملء جميع الخانات المعتمدة  |  هل فعال يقبل: نعم / لا  |  رموز المنطقة والفرع تاتي من جدول الترميز  |  الخلية المغذية تطابق عداد الخلية</t>
+          <t>يرجى التاكد من ملء جميع الخانات المعتمدة  |  هل فعال يقبل: نعم / لا  |  رموز المنطقة والفرع اختياريان (يمكن تركهما فارغين)  |  الخلية المغذية تطابق عداد الخلية</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -659,12 +659,12 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>رمز المنطقة *</t>
+          <t>رمز المنطقة</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>رمز الفرع *</t>
+          <t>رمز الفرع</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -793,16 +793,8 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>HOD</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>ZBD</t>
-        </is>
-      </c>
+      <c r="A6" s="15" t="inlineStr"/>
+      <c r="B6" s="15" t="inlineStr"/>
       <c r="C6" s="15" t="inlineStr">
         <is>
           <t>نعم</t>
@@ -908,7 +900,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>3. رمزا المنطقة والفرع يجب أن يطابقا جدول الترميز الموجود في النظام.</t>
+          <t>3. رمزا المنطقة والفرع اختياريان (يمكن تركهما فارغين أو التطابق لاحقاً).</t>
         </is>
       </c>
     </row>

--- a/utility_core/static/src/Transformer_Migration_Template.xlsx
+++ b/utility_core/static/src/Transformer_Migration_Template.xlsx
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -287,6 +287,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -728,82 +734,82 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>رمز المنطقة</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>رمز الفرع</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>هل فعال؟ *</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>رمز المحول *</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>اسم المحول *</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>رقم عداد رصد المحول</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>معامل الضرب للعداد</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>القراءة الحالية</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>إجمالي الاستهلاك</t>
         </is>
       </c>
-      <c r="J4" s="20" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>حالة الصورة</t>
         </is>
       </c>
-      <c r="K4" s="20" t="inlineStr">
+      <c r="K4" s="28" t="inlineStr">
         <is>
           <t>رقم عداد الخلية المغذية</t>
         </is>
       </c>
-      <c r="L4" s="20" t="inlineStr">
+      <c r="L4" s="28" t="inlineStr">
         <is>
           <t>معامل ضرب عداد الخلية</t>
         </is>
       </c>
-      <c r="M4" s="20" t="inlineStr">
+      <c r="M4" s="28" t="inlineStr">
         <is>
           <t>المرجع</t>
         </is>
       </c>
-      <c r="N4" s="20" t="inlineStr">
+      <c r="N4" s="28" t="inlineStr">
         <is>
           <t>الوصف</t>
         </is>
       </c>
-      <c r="O4" s="22" t="inlineStr">
+      <c r="O4" s="29" t="inlineStr">
         <is>
           <t>قراءة بداية الاشتراك</t>
         </is>
       </c>
-      <c r="P4" s="22" t="inlineStr">
+      <c r="P4" s="29" t="inlineStr">
         <is>
           <t>معرف الحساب التحليلي</t>
         </is>
@@ -14834,20 +14840,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>تعليمات الاستيراد — عقد ترحيل رسمي</t>
+          <t>تعليمات استيراد المحولات — عقد v3</t>
         </is>
       </c>
-      <c r="B1" s="26" t="n"/>
+      <c r="B1" s="26" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
@@ -14857,7 +14863,7 @@
       </c>
       <c r="B2" s="26" t="inlineStr">
         <is>
-          <t>Transformer_Migration_Template</t>
+          <t>transformer</t>
         </is>
       </c>
     </row>
@@ -14868,126 +14874,54 @@
         </is>
       </c>
       <c r="B3" s="26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>نوع الملف</t>
+          <t>الهوية</t>
         </is>
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>.xlsx فقط — لا تستخدم .xls</t>
+          <t>reference ثم transformer_code ثم legacy_analytic_id؛ لا تستخدم الاسم أو الوصف.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>الحقول الإلزامية</t>
+          <t>القراءات</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>رمز المحول *، اسم المحول *، رقم عداد رصد المحول</t>
+          <t>current_reading له الأولوية على opening_reading؛ الفراغ لا ينشئ قراءة.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>الحقول الاختيارية</t>
+          <t>القيم</t>
         </is>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>تُترك فارغة عند عدم توفرها، ولا تحذف العناوين</t>
+          <t>المعامل أكبر من صفر، والقراءات والاستهلاك غير سالبة. الفراغ ليس صفراً.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>قواعد الهوية</t>
+          <t>تنبيه</t>
         </is>
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>reference ثم transformer_code ثم legacy_analytic_id؛ لا تستخدم الاسم أو الوصف.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>القراءات</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>current_reading له الأولوية على opening_reading؛ الفراغ لا ينشئ قراءة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>القيم المنطقية</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>TRUE/FALSE أو نعم/لا أو 1/0 أو yes/no فقط؛ القيمة غير المعروفة خطأ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>الطور</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>single أو three فقط؛ القيمة غير المعروفة خطأ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>الأرقام</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>القراءات والمعاملات أرقام حقيقية غير سالبة؛ الفراغ ليس صفرًا، والصفر قيمة صحيحة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>تنبيه</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>لا تغيّر أسماء العناوين، لا تدمج خلايا البيانات، لا تضف صيغًا، وحافظ على الأصفار البادئة للمعرفات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>reference=TR-001، opening_reading=150.5.</t>
+          <t>لا تغيّر العناوين، لا تدمج خلايا Data، لا تستخدم صيغاً، واحفظ الأصفار البادئة.</t>
         </is>
       </c>
     </row>
